--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -14391,10 +14391,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118378071</v>
+        <v>118378082</v>
       </c>
       <c r="B118" t="n">
-        <v>77421</v>
+        <v>96964</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14403,25 +14403,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228579</v>
+        <v>222741</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14431,10 +14431,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>404995</v>
+        <v>404711</v>
       </c>
       <c r="R118" t="n">
-        <v>7051381</v>
+        <v>7051515</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14477,16 +14477,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>granbas</t>
-        </is>
-      </c>
-      <c r="AP118" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14503,10 +14493,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118378082</v>
+        <v>118378071</v>
       </c>
       <c r="B119" t="n">
-        <v>96964</v>
+        <v>77421</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14515,25 +14505,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222741</v>
+        <v>228579</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14543,10 +14533,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>404711</v>
+        <v>404995</v>
       </c>
       <c r="R119" t="n">
-        <v>7051515</v>
+        <v>7051381</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14589,6 +14579,16 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">

--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -14177,10 +14177,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118378068</v>
+        <v>118378082</v>
       </c>
       <c r="B116" t="n">
-        <v>79022</v>
+        <v>96964</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14189,25 +14189,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1353</v>
+        <v>222741</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14217,10 +14217,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>404995</v>
+        <v>404711</v>
       </c>
       <c r="R116" t="n">
-        <v>7051381</v>
+        <v>7051515</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14263,11 +14263,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>grankvist</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -14391,10 +14386,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118378082</v>
+        <v>118378083</v>
       </c>
       <c r="B118" t="n">
-        <v>96964</v>
+        <v>78647</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14403,25 +14398,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222741</v>
+        <v>1249</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14477,6 +14472,11 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14493,10 +14493,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118378071</v>
+        <v>118378070</v>
       </c>
       <c r="B119" t="n">
-        <v>77421</v>
+        <v>74596</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14509,21 +14509,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14582,12 +14582,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>granbas</t>
-        </is>
-      </c>
-      <c r="AP119" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14605,10 +14600,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118378083</v>
+        <v>118378073</v>
       </c>
       <c r="B120" t="n">
-        <v>78647</v>
+        <v>74528</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14621,21 +14616,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1249</v>
+        <v>1776</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14645,10 +14640,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>404711</v>
+        <v>404995</v>
       </c>
       <c r="R120" t="n">
-        <v>7051515</v>
+        <v>7051381</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14694,7 +14689,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14712,10 +14707,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118378073</v>
+        <v>118378071</v>
       </c>
       <c r="B121" t="n">
-        <v>74528</v>
+        <v>77421</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14724,25 +14719,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1776</v>
+        <v>228579</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14801,7 +14796,12 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118378070</v>
+        <v>118378068</v>
       </c>
       <c r="B122" t="n">
-        <v>74596</v>
+        <v>79022</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>1353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -14070,10 +14070,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118378074</v>
+        <v>118378082</v>
       </c>
       <c r="B115" t="n">
-        <v>74580</v>
+        <v>96964</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6439</v>
+        <v>222741</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>404995</v>
+        <v>404711</v>
       </c>
       <c r="R115" t="n">
-        <v>7051381</v>
+        <v>7051515</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14156,11 +14156,6 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>grankvist</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -14177,10 +14172,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118378082</v>
+        <v>118378083</v>
       </c>
       <c r="B116" t="n">
-        <v>96964</v>
+        <v>78647</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14189,25 +14184,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222741</v>
+        <v>1249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14263,6 +14258,11 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -14386,10 +14386,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118378083</v>
+        <v>118378071</v>
       </c>
       <c r="B118" t="n">
-        <v>78647</v>
+        <v>77421</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14398,25 +14398,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14426,10 +14426,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>404711</v>
+        <v>404995</v>
       </c>
       <c r="R118" t="n">
-        <v>7051515</v>
+        <v>7051381</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14475,7 +14475,12 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14493,10 +14498,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118378070</v>
+        <v>118378073</v>
       </c>
       <c r="B119" t="n">
-        <v>74596</v>
+        <v>74528</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14505,25 +14510,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>1776</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14582,7 +14587,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14600,10 +14605,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118378073</v>
+        <v>118378074</v>
       </c>
       <c r="B120" t="n">
-        <v>74528</v>
+        <v>74580</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14612,25 +14617,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1776</v>
+        <v>6439</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14707,10 +14712,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118378071</v>
+        <v>118378068</v>
       </c>
       <c r="B121" t="n">
-        <v>77421</v>
+        <v>79022</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14719,25 +14724,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228579</v>
+        <v>1353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14796,12 +14801,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>granbas</t>
-        </is>
-      </c>
-      <c r="AP121" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118378068</v>
+        <v>118378070</v>
       </c>
       <c r="B122" t="n">
-        <v>79022</v>
+        <v>74596</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1353</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -14070,10 +14070,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118378082</v>
+        <v>118378083</v>
       </c>
       <c r="B115" t="n">
-        <v>96964</v>
+        <v>78654</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14082,25 +14082,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222741</v>
+        <v>1249</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14156,6 +14156,11 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -14172,10 +14177,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118378083</v>
+        <v>118378068</v>
       </c>
       <c r="B116" t="n">
-        <v>78647</v>
+        <v>79029</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14184,25 +14189,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1249</v>
+        <v>1353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14212,10 +14217,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>404711</v>
+        <v>404995</v>
       </c>
       <c r="R116" t="n">
-        <v>7051515</v>
+        <v>7051381</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14261,7 +14266,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14279,10 +14284,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118378072</v>
+        <v>118378071</v>
       </c>
       <c r="B117" t="n">
-        <v>78568</v>
+        <v>77428</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14295,21 +14300,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14368,7 +14373,12 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14386,10 +14396,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118378071</v>
+        <v>118378073</v>
       </c>
       <c r="B118" t="n">
-        <v>77421</v>
+        <v>74535</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14398,25 +14408,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228579</v>
+        <v>1776</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14475,12 +14485,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>granbas</t>
-        </is>
-      </c>
-      <c r="AP118" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14498,10 +14503,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118378073</v>
+        <v>118378072</v>
       </c>
       <c r="B119" t="n">
-        <v>74528</v>
+        <v>78575</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14510,25 +14515,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1776</v>
+        <v>283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14608,7 +14613,7 @@
         <v>118378074</v>
       </c>
       <c r="B120" t="n">
-        <v>74580</v>
+        <v>74587</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14712,10 +14717,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118378068</v>
+        <v>118378070</v>
       </c>
       <c r="B121" t="n">
-        <v>79022</v>
+        <v>74603</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14724,25 +14729,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1353</v>
+        <v>6440</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14801,7 +14806,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14819,10 +14824,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118378070</v>
+        <v>118378082</v>
       </c>
       <c r="B122" t="n">
-        <v>74596</v>
+        <v>96971</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14831,25 +14836,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>222741</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14859,10 +14864,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>404995</v>
+        <v>404711</v>
       </c>
       <c r="R122" t="n">
-        <v>7051381</v>
+        <v>7051515</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14905,11 +14910,6 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">

--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -14070,10 +14070,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118378083</v>
+        <v>118378072</v>
       </c>
       <c r="B115" t="n">
-        <v>78654</v>
+        <v>78575</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14082,25 +14082,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>404711</v>
+        <v>404995</v>
       </c>
       <c r="R115" t="n">
-        <v>7051515</v>
+        <v>7051381</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14177,10 +14177,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118378068</v>
+        <v>118378070</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>74603</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14189,25 +14189,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1353</v>
+        <v>6440</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14284,10 +14284,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118378071</v>
+        <v>118378073</v>
       </c>
       <c r="B117" t="n">
-        <v>77428</v>
+        <v>74535</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14296,25 +14296,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>1776</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14373,12 +14373,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>granbas</t>
-        </is>
-      </c>
-      <c r="AP117" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14396,10 +14391,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118378073</v>
+        <v>118378082</v>
       </c>
       <c r="B118" t="n">
-        <v>74535</v>
+        <v>96971</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14408,25 +14403,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1776</v>
+        <v>222741</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14436,10 +14431,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>404995</v>
+        <v>404711</v>
       </c>
       <c r="R118" t="n">
-        <v>7051381</v>
+        <v>7051515</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14482,11 +14477,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>grankvist</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14503,10 +14493,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118378072</v>
+        <v>118378083</v>
       </c>
       <c r="B119" t="n">
-        <v>78575</v>
+        <v>78654</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14515,25 +14505,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14543,10 +14533,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>404995</v>
+        <v>404711</v>
       </c>
       <c r="R119" t="n">
-        <v>7051381</v>
+        <v>7051515</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14592,7 +14582,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14610,10 +14600,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118378074</v>
+        <v>118378071</v>
       </c>
       <c r="B120" t="n">
-        <v>74587</v>
+        <v>77428</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14622,25 +14612,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14699,7 +14689,12 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>grankvist</t>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14717,10 +14712,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118378070</v>
+        <v>118378074</v>
       </c>
       <c r="B121" t="n">
-        <v>74603</v>
+        <v>74587</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14729,25 +14724,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14806,7 +14801,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>grankvist</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14824,10 +14819,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118378082</v>
+        <v>118378068</v>
       </c>
       <c r="B122" t="n">
-        <v>96971</v>
+        <v>79029</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14836,25 +14831,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222741</v>
+        <v>1353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14864,10 +14859,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>404711</v>
+        <v>404995</v>
       </c>
       <c r="R122" t="n">
-        <v>7051515</v>
+        <v>7051381</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14910,6 +14905,11 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>grankvist</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">

--- a/artfynd/A 10635-2023 artfynd.xlsx
+++ b/artfynd/A 10635-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY154"/>
+  <dimension ref="A1:AZ154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99727617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240145</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240157</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378072</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240124</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566166</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109504159</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,6 +1601,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99727615</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1653,6 +1703,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240178</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1847,6 +1907,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396509</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1944,6 +2009,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102152227</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2041,6 +2111,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102152228</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2138,6 +2213,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240172</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109505885</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2334,6 +2419,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109506091</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378083</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102152230</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2635,6 +2735,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566168</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2737,6 +2842,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99727622</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240183</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2931,6 +3046,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240186</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3033,6 +3153,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378068</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3130,6 +3255,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240190</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3232,6 +3362,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99727620</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3329,6 +3464,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102152229</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3455,6 +3595,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650081</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3571,6 +3716,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103493066</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3673,6 +3823,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566172</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3770,6 +3925,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240112</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3867,6 +4027,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240113</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3964,6 +4129,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240126</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4061,6 +4231,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240127</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4158,6 +4333,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240131</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4256,6 +4436,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240136</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4353,6 +4538,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240144</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4450,6 +4640,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240150</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4547,6 +4742,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240156</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4644,6 +4844,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240158</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4741,6 +4946,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240165</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4838,6 +5048,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240174</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4935,6 +5150,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240175</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5032,6 +5252,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240179</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5129,6 +5354,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240181</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5226,6 +5456,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240187</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5323,6 +5558,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240189</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5420,6 +5660,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240192</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5518,6 +5763,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109504403</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5620,6 +5870,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378073</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5758,6 +6013,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650074</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5865,6 +6125,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566142</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5962,6 +6227,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396553</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6059,6 +6329,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240125</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6156,6 +6431,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240135</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6253,6 +6533,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240188</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6355,6 +6640,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378074</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6457,6 +6747,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566171</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6554,6 +6849,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240129</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6651,6 +6951,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240140</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6753,6 +7058,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378070</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6850,6 +7160,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99727618</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6966,6 +7281,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911833</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7063,6 +7383,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396552</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7160,6 +7485,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240132</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7270,6 +7600,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305616</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7380,6 +7715,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305617</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7490,6 +7830,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305623</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7600,6 +7945,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305624</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7710,6 +8060,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305625</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7820,6 +8175,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305626</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7930,6 +8290,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305627</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8040,6 +8405,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305628</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8150,6 +8520,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305630</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8260,6 +8635,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305631</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8370,6 +8750,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305633</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8480,6 +8865,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396515</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8590,6 +8980,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396517</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8700,6 +9095,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396518</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8810,6 +9210,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396519</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8920,6 +9325,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396520</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9030,6 +9440,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396521</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9140,6 +9555,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396522</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9250,6 +9670,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396523</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9360,6 +9785,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396525</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9470,6 +9900,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396526</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9580,6 +10015,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396527</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9690,6 +10130,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396528</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9800,6 +10245,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396529</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9910,6 +10360,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396534</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10020,6 +10475,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396537</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10130,6 +10590,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396538</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10240,6 +10705,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396539</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10350,6 +10820,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396540</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10460,6 +10935,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396543</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10570,6 +11050,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396544</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10680,6 +11165,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396545</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10790,6 +11280,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396546</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10900,6 +11395,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396547</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11010,6 +11510,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396548</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11120,6 +11625,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396549</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11230,6 +11740,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396550</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11340,6 +11855,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396551</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11450,6 +11970,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104512080</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11560,6 +12085,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104512089</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11670,6 +12200,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104512090</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11777,6 +12312,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240111</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11884,6 +12424,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240116</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11991,6 +12536,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240121</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12098,6 +12648,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240137</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12205,6 +12760,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240146</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12312,6 +12872,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240152</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12419,6 +12984,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240153</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12526,6 +13096,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240154</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12633,6 +13208,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240171</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12740,6 +13320,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240180</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12847,6 +13432,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240194</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12953,6 +13543,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312674</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13059,6 +13654,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312675</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13169,6 +13769,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312676</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13275,6 +13880,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312677</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13381,6 +13991,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312678</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13491,6 +14106,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312681</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13597,6 +14217,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312682</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13703,6 +14328,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312712</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13813,6 +14443,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312713</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13919,6 +14554,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312714</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14025,6 +14665,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312715</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14135,6 +14780,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312716</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14245,6 +14895,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312717</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14355,6 +15010,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312718</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14461,6 +15121,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312719</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14567,6 +15232,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312720</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14677,6 +15347,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312721</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14783,6 +15458,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312722</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14889,6 +15569,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312723</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14999,6 +15684,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312748</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15096,6 +15786,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396562</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15201,6 +15896,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396556</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15298,6 +15998,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396557</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15395,6 +16100,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378082</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15492,6 +16202,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240193</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15599,6 +16314,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378071</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15696,6 +16416,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240149</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15817,6 +16542,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102650079</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15928,6 +16658,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911841</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16039,6 +16774,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102911861</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16131,6 +16871,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240142</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16223,6 +16968,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240148</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16315,6 +17065,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240155</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16407,6 +17162,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240166</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16499,6 +17259,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240173</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16592,8 +17357,168 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109508866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>